--- a/assets/libreoffice_calc_njc/8ffd2449-cdc1-46a5-8c8d-e909fbe3fc70/ProjStatus_L2_09.xlsx
+++ b/assets/libreoffice_calc_njc/8ffd2449-cdc1-46a5-8c8d-e909fbe3fc70/ProjStatus_L2_09.xlsx
@@ -300,8 +300,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -323,324 +327,324 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>35000</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>80000</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>72000</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>45000</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>18000</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>35000</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>55000</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="H8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="0" t="s">
+      <c r="I8" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>45000</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="0" t="s">
+      <c r="H9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="0" t="s">
+      <c r="H10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="0" t="s">
+      <c r="I10" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>15000</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="0" t="s">
+      <c r="H11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="0" t="s">
+      <c r="I11" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -661,61 +665,61 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>395000</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>253000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>35000</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>10000</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/8ffd2449-cdc1-46a5-8c8d-e909fbe3fc70/ProjStatus_L2_09.xlsx
+++ b/assets/libreoffice_calc_njc/8ffd2449-cdc1-46a5-8c8d-e909fbe3fc70/ProjStatus_L2_09.xlsx
@@ -665,7 +665,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/assets/libreoffice_calc_njc/8ffd2449-cdc1-46a5-8c8d-e909fbe3fc70/ProjStatus_L2_09.xlsx
+++ b/assets/libreoffice_calc_njc/8ffd2449-cdc1-46a5-8c8d-e909fbe3fc70/ProjStatus_L2_09.xlsx
@@ -9,7 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="StatusSummary" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="StatussSummary" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="StatusSummary" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
   <si>
     <t xml:space="preserve">Project ID</t>
   </si>
@@ -225,14 +227,24 @@
   </si>
   <si>
     <t xml:space="preserve">Total Spent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Hold</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -300,12 +312,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -664,7 +680,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -681,46 +697,72 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">COUNTIF(Projects!A:A,"Complete")</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="e">
+        <f aca="false">sumr=SUMIF(projects A:A, A2, projects D:D)oject(projects A:A, A2, projects D:D)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D2" s="2" t="e">
+        <f aca="false">SUMIF(projects A:A, A2, projects E:E)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>395000</v>
+        <f aca="false">COUNTIF(Projects!A:A,"In Progress")</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="e">
+        <f aca="false">SUMIF(projects A:A, A2, projects D:D)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>253000</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">SUMIF(Projects!A:A,"In Progress",Projects!D:D)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>35000</v>
+        <f aca="false">COUNTIF(Projects!A:A,"Not Started")</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="e">
+        <f aca="false">SUMIF(projects A:A, A2, projects D:D)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>10000</v>
+        <f aca="false">SUMIF(Projects!A:A,"On Hold",Projects!D:D)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <f aca="false">COUNTIF(Projects!A:A,"On Hold")</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="e">
+        <f aca="false">SUMIF(projects A:A, A2, projects D:D)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <f aca="false">SUMIF(Projects!B:B,"Complete",Projects!F:F)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -732,4 +774,97 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>395000</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>253000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>